--- a/templates/payroll_template.xlsx
+++ b/templates/payroll_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\htdocs\Payroll\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397502A7-2042-47CA-BAD8-812E673AA3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EC689C-61B4-46B9-85E8-11856E6DC109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
     <t>Uang Makan/Seragam</t>
   </si>
   <si>
-    <t>PT. SARDANA INDAHBERLIAN MOTOR</t>
+    <t>No.</t>
   </si>
 </sst>
 </file>
@@ -126,7 +126,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -149,19 +149,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -444,116 +479,119 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="4"/>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5">
-        <v>46296</v>
-      </c>
-      <c r="C2" s="5"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="P5" s="1"/>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q5" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B2:C2"/>
+  <mergeCells count="4">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/payroll_template.xlsx
+++ b/templates/payroll_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\htdocs\Payroll\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EC689C-61B4-46B9-85E8-11856E6DC109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E92980-80B4-404F-9B15-EF93ACD114F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
     <t>Uang Makan/Seragam</t>
   </si>
   <si>
-    <t>No.</t>
+    <t>No</t>
   </si>
 </sst>
 </file>
